--- a/returns.xlsx
+++ b/returns.xlsx
@@ -4188,7 +4188,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemistry Med Easy | Notes, Formulas, Tips &amp; Tricks for NEET/JEE &amp; Board Exams | Pankaj Sir Chemistry Handwritten Notes</t>
+          <t xml:space="preserve">Chemistry Med Easy | Notes, Formulas, Tips &amp; Tricks for NEET/JEE &amp; Board Exams | Pankaj Sir Chemistry Handwritten Notes!</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemistry Med Easy | Notes, Formulas, Tips &amp; Tricks for NEET/JEE &amp; Board Exams | Pankaj Sir Chemistry Handwritten Notes</t>
+          <t xml:space="preserve">Chemistry Med Easy | Notes, Formulas, Tips &amp; Tricks for NEET/JEE &amp; Board Exams | Pankaj Sir Chemistry Handwritten Notes!</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Zoology Med Easy 2.0 For NEET and Board Exams 2025-26 | Flowcharts, Schematic Diagrams l Samapti Sinha Mahapatra Handwritten Notes</t>
+          <t xml:space="preserve">Zoology Med Easy 2.0 For NEET and Board Exams 2025-26 | Flowcharts, Schematic Diagrams l Samapti Sinha Mahapatra Handwritten Notes!</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -27852,7 +27852,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Absolute JEE Advanced Mathematics 2500+ Questions with Formula Sheet Latest Solved Paper and 3 Mock Tests | Covering All JEE Advanced Question Typology</t>
+          <t xml:space="preserve">Absolute JEE Advanced Mathematics 2500+ Questions with Formula Sheet Latest Solved Paper and 3 Mock Tests | Covering All JEE Advanced Question Typology--</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -31660,7 +31660,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Zoology Med Easy 2.0 For NEET and Board Exams 2025-26 | Flowcharts, Schematic Diagrams l Samapti Sinha Mahapatra Handwritten Notes</t>
+          <t xml:space="preserve">Zoology Med Easy 2.0 For NEET and Board Exams 2025-26 | Flowcharts, Schematic Diagrams l Samapti Sinha Mahapatra Handwritten Notes!</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -31932,7 +31932,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemistry Med Easy | Notes, Formulas, Tips &amp; Tricks for NEET/JEE &amp; Board Exams | Pankaj Sir Chemistry Handwritten Notes</t>
+          <t xml:space="preserve">Chemistry Med Easy | Notes, Formulas, Tips &amp; Tricks for NEET/JEE &amp; Board Exams | Pankaj Sir Chemistry Handwritten Notes!</t>
         </is>
       </c>
       <c t="inlineStr">

--- a/returns.xlsx
+++ b/returns.xlsx
@@ -1246,7 +1246,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">2.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">2.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">2.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">2.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">2.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">1.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">4.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">6.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">9.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">3.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">1.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">5.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">10.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">10.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">2.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">1.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">2.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">1.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">1.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">1.000</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">0.000</t>
+          <t xml:space="preserve">1.000</t>
         </is>
       </c>
       <c t="inlineStr">
